--- a/SNOW Model.xlsx
+++ b/SNOW Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Financial Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EF128A-AEC4-4E87-B290-A30C33DAF850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F6A84C-341A-4AA6-BBB2-56C47AE14B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="61656" windowHeight="16896" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
+    <workbookView xWindow="31920" yWindow="2184" windowWidth="26172" windowHeight="14028" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -962,38 +962,38 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>280.67</v>
+    <v>384.56</v>
     <v>118.3</v>
-    <v>1.3536999999999999</v>
-    <v>16.350000000000001</v>
-    <v>0</v>
-    <v>6.8352999999999997E-2</v>
-    <v>0</v>
+    <v>1.3163</v>
+    <v>11.47</v>
+    <v>1.5359999999999999E-4</v>
+    <v>3.6533000000000003E-2</v>
+    <v>0.05</v>
     <v>USD</v>
     <v>Snowflake Inc. is an artificial intelligence (AI) data cloud company. The Company provides a platform which powers the AI data cloud, enabling customers to consolidate data into a single source of truth to drive insights, apply AI to solve business problems, build data applications, and share data and data products. Its cloud-native architecture includes three independently scalable but logically integrated layers across storage, compute, and cloud services. The storage layer ingests massive amounts and varieties of structured, semi-structured, and unstructured data. The compute layer provides dedicated resources to enable users to simultaneously access common data sets for many use cases with minimal latency. The cloud services layer enables users to securely use AI within applications, tools, and processes. Its platform supports a wide range of product categories for customers’ business objectives, including analytics, data engineering, AI, applications and collaboration.</v>
     <v>9060</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
-    <v>106 East Babcock Street, Suite 3A, BOZEMAN, MT, 59715 US</v>
-    <v>256.20999999999998</v>
+    <v>135 Constitution Drive, MENLO PARK, CA, 94025 US</v>
+    <v>325.62</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46171.999680890622</v>
+    <v>46318.999725277346</v>
     <v>0</v>
-    <v>239.5</v>
-    <v>60745624254</v>
+    <v>310.31</v>
+    <v>114811704000</v>
     <v>SNOWFLAKE INC.</v>
     <v>SNOWFLAKE INC.</v>
-    <v>240.69</v>
-    <v>239.2</v>
-    <v>255.55</v>
-    <v>255.55</v>
-    <v>346602900</v>
+    <v>310.31</v>
+    <v>313.95999999999998</v>
+    <v>325.43</v>
+    <v>325.48</v>
+    <v>352800000</v>
     <v>SNOW</v>
     <v>SNOWFLAKE INC. (XNYS:SNOW)</v>
-    <v>19892241</v>
-    <v>9204231</v>
+    <v>3136249</v>
+    <v>4407836</v>
     <v>2012</v>
   </rv>
   <rv s="2">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="P7" s="7">
         <f>SUM(K116:P116)</f>
-        <v>3891.2590974103773</v>
+        <v>3971.9821487566414</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>33</v>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E8" s="18">
         <f>U12</f>
-        <v>207.04678114834698</v>
+        <v>209.92834036841444</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>47</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="P8" s="7">
         <f>P27*U8</f>
-        <v>131019.35549835263</v>
+        <v>132868.22214868799</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>86</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E9" s="18">
         <f ca="1">Extras!C2</f>
-        <v>255.55</v>
+        <v>325.43</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>48</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="P9" s="7">
         <f>P8/(1+$U$7)^(P115+0.5)</f>
-        <v>75059.377057064194</v>
+        <v>76118.570017584425</v>
       </c>
       <c r="U9" s="7"/>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E10" s="29">
         <f ca="1">E8/E9-1</f>
-        <v>-0.18979933027451779</v>
+        <v>-0.35492013530278577</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>49</v>
@@ -1863,14 +1863,14 @@
       </c>
       <c r="P12" s="7">
         <f>(P9+P7-P10)</f>
-        <v>81905.636154474574</v>
+        <v>83045.552166341062</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>67</v>
       </c>
       <c r="U12" s="35">
         <f>P12/P11</f>
-        <v>207.04678114834698</v>
+        <v>209.92834036841444</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2166,28 +2166,28 @@
         <v>4683.9459999999999</v>
       </c>
       <c r="K27" s="7">
-        <f>J27*1.32</f>
-        <v>6182.80872</v>
+        <f>J27*1.34</f>
+        <v>6276.4876400000003</v>
       </c>
       <c r="L27" s="7">
-        <f>K27*1.28</f>
-        <v>7913.9951615999998</v>
+        <f>K27*1.3</f>
+        <v>8159.4339320000008</v>
       </c>
       <c r="M27" s="7">
         <f>L27*1.25</f>
-        <v>9892.4939520000007</v>
+        <v>10199.292415000002</v>
       </c>
       <c r="N27" s="7">
-        <f>M27*1.22</f>
-        <v>12068.842621440001</v>
+        <f>M27*1.2</f>
+        <v>12239.150898000002</v>
       </c>
       <c r="O27" s="7">
         <f>N27*1.18</f>
-        <v>14241.2342932992</v>
+        <v>14442.198059640001</v>
       </c>
       <c r="P27" s="7">
         <f>O27*1.15</f>
-        <v>16377.419437294078</v>
+        <v>16608.527768585998</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2222,11 +2222,11 @@
       </c>
       <c r="K28" s="10">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="L28" s="10">
         <f t="shared" ref="L28" si="1">(L27-K27)/K27</f>
-        <v>0.27999999999999997</v>
+        <v>0.3000000000000001</v>
       </c>
       <c r="M28" s="10">
         <f t="shared" ref="M28:N28" si="2">(M27-L27)/L27</f>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="N28" s="10">
         <f t="shared" si="2"/>
-        <v>0.21999999999999997</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O28" s="10">
         <f t="shared" ref="O28" si="3">(O27-N27)/N27</f>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="P28" s="10">
         <f t="shared" ref="P28" si="4">(P27-O27)/O27</f>
-        <v>0.14999999999999991</v>
+        <v>0.14999999999999983</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="K30" s="7">
         <f>K27*0.32</f>
-        <v>1978.4987904</v>
+        <v>2008.4760448000002</v>
       </c>
       <c r="L30" s="7">
         <f>L27*0.31</f>
-        <v>2453.3385000959997</v>
+        <v>2529.4245189200001</v>
       </c>
       <c r="M30" s="7">
         <f>M27*0.3</f>
-        <v>2967.7481855999999</v>
+        <v>3059.7877245000004</v>
       </c>
       <c r="N30" s="7">
         <f>N27*0.29</f>
-        <v>3499.9643602175997</v>
+        <v>3549.3537604200001</v>
       </c>
       <c r="O30" s="7">
         <f>O27*0.28</f>
-        <v>3987.5456021237765</v>
+        <v>4043.8154566992007</v>
       </c>
       <c r="P30" s="7">
         <f>P27*0.27</f>
-        <v>4421.9032480694013</v>
+        <v>4484.3024975182198</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2391,27 +2391,27 @@
       </c>
       <c r="K33" s="7">
         <f t="shared" si="12"/>
-        <v>4204.3099296</v>
+        <v>4268.0115951999996</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="12"/>
-        <v>5460.6566615040001</v>
+        <v>5630.0094130800007</v>
       </c>
       <c r="M33" s="7">
         <f t="shared" si="12"/>
-        <v>6924.7457664000012</v>
+        <v>7139.5046905000017</v>
       </c>
       <c r="N33" s="7">
         <f t="shared" si="12"/>
-        <v>8568.8782612224004</v>
+        <v>8689.7971375800007</v>
       </c>
       <c r="O33" s="7">
         <f t="shared" si="12"/>
-        <v>10253.688691175423</v>
+        <v>10398.382602940801</v>
       </c>
       <c r="P33" s="7">
         <f t="shared" si="12"/>
-        <v>11955.516189224676</v>
+        <v>12124.225271067779</v>
       </c>
     </row>
     <row r="34" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K34" s="10">
         <f t="shared" ref="K34" si="18">K33/K$27</f>
-        <v>0.68</v>
+        <v>0.67999999999999994</v>
       </c>
       <c r="L34" s="10">
         <f t="shared" ref="L34" si="19">L33/L$27</f>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="O34" s="10">
         <f t="shared" ref="O34" si="22">O33/O$27</f>
-        <v>0.72</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="P34" s="10">
         <f t="shared" ref="P34" si="23">P33/P$27</f>
@@ -2492,27 +2492,27 @@
       </c>
       <c r="K36" s="7">
         <f>K27*0.41</f>
-        <v>2534.9515751999998</v>
+        <v>2573.3599324000002</v>
       </c>
       <c r="L36" s="7">
         <f>L27*0.38</f>
-        <v>3007.3181614079999</v>
+        <v>3100.5848941600002</v>
       </c>
       <c r="M36" s="7">
         <f>M27*0.35</f>
-        <v>3462.3728832000002</v>
+        <v>3569.7523452500004</v>
       </c>
       <c r="N36" s="7">
         <f>N27*0.32</f>
-        <v>3862.0296388608003</v>
+        <v>3916.5282873600008</v>
       </c>
       <c r="O36" s="7">
         <f>O27*0.29</f>
-        <v>4129.957945056768</v>
+        <v>4188.2374372956001</v>
       </c>
       <c r="P36" s="7">
         <f>P27*0.26</f>
-        <v>4258.1290536964607</v>
+        <v>4318.2172198323597</v>
       </c>
     </row>
     <row r="37" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="K37" s="10">
         <f t="shared" ref="K37" si="29">K36/K$27</f>
-        <v>0.41</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" ref="L37" si="30">L36/L$27</f>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" ref="O37" si="33">O36/O$27</f>
-        <v>0.29000000000000004</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P37" s="10">
         <f t="shared" ref="P37" si="34">P36/P$27</f>
@@ -2597,27 +2597,27 @@
       </c>
       <c r="K39" s="7">
         <f>K27*0.39</f>
-        <v>2411.2954008000002</v>
+        <v>2447.8301796000001</v>
       </c>
       <c r="L39" s="7">
         <f>L27*0.36</f>
-        <v>2849.038258176</v>
+        <v>2937.3962155200002</v>
       </c>
       <c r="M39" s="7">
         <f>M27*0.33</f>
-        <v>3264.5230041600003</v>
+        <v>3365.7664969500006</v>
       </c>
       <c r="N39" s="7">
         <f>N27*0.3</f>
-        <v>3620.6527864320001</v>
+        <v>3671.7452694000003</v>
       </c>
       <c r="O39" s="7">
         <f>O27*0.27</f>
-        <v>3845.133259190784</v>
+        <v>3899.3934761028004</v>
       </c>
       <c r="P39" s="7">
         <f>P27*0.25</f>
-        <v>4094.3548593235196</v>
+        <v>4152.1319421464996</v>
       </c>
     </row>
     <row r="40" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="K42" s="7">
         <f>K27*0.11</f>
-        <v>680.10895919999996</v>
+        <v>690.41364040000008</v>
       </c>
       <c r="L42" s="7">
         <f>L27*0.1</f>
-        <v>791.39951616000008</v>
+        <v>815.94339320000017</v>
       </c>
       <c r="M42" s="7">
         <f>M27*0.09</f>
-        <v>890.32445568000003</v>
+        <v>917.93631735000008</v>
       </c>
       <c r="N42" s="7">
         <f>N27*0.08</f>
-        <v>965.50740971520008</v>
+        <v>979.13207184000021</v>
       </c>
       <c r="O42" s="7">
         <f>O27*0.075</f>
-        <v>1068.09257199744</v>
+        <v>1083.1648544730001</v>
       </c>
       <c r="P42" s="7">
         <f>P27*0.07</f>
-        <v>1146.4193606105855</v>
+        <v>1162.59694380102</v>
       </c>
     </row>
     <row r="43" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="K43" s="10">
         <f t="shared" ref="K43" si="51">K42/K$27</f>
-        <v>0.10999999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="L43" s="10">
         <f t="shared" ref="L43" si="52">L42/L$27</f>
@@ -2816,27 +2816,27 @@
       </c>
       <c r="K45" s="28">
         <f t="shared" ref="K45:P45" si="58">K33-K36-K39-K42</f>
-        <v>-1422.0460055999997</v>
+        <v>-1443.5921572000007</v>
       </c>
       <c r="L45" s="28">
         <f t="shared" si="58"/>
-        <v>-1187.0992742399999</v>
+        <v>-1223.9150897999998</v>
       </c>
       <c r="M45" s="28">
         <f t="shared" si="58"/>
-        <v>-692.47457663999921</v>
+        <v>-713.95046904999936</v>
       </c>
       <c r="N45" s="28">
         <f t="shared" si="58"/>
-        <v>120.6884262143999</v>
+        <v>122.39150897999934</v>
       </c>
       <c r="O45" s="28">
         <f t="shared" si="58"/>
-        <v>1210.5049149304307</v>
+        <v>1227.5868350694004</v>
       </c>
       <c r="P45" s="28">
         <f t="shared" si="58"/>
-        <v>2456.6129155941103</v>
+        <v>2491.2791652878996</v>
       </c>
     </row>
     <row r="46" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2869,27 +2869,27 @@
       </c>
       <c r="K46" s="29">
         <f t="shared" ref="K46" si="64">K45/K$27</f>
-        <v>-0.22999999999999995</v>
+        <v>-0.23000000000000009</v>
       </c>
       <c r="L46" s="29">
         <f t="shared" ref="L46" si="65">L45/L$27</f>
-        <v>-0.15</v>
+        <v>-0.14999999999999997</v>
       </c>
       <c r="M46" s="29">
         <f t="shared" ref="M46" si="66">M45/M$27</f>
-        <v>-6.999999999999991E-2</v>
+        <v>-6.9999999999999923E-2</v>
       </c>
       <c r="N46" s="29">
         <f t="shared" ref="N46" si="67">N45/N$27</f>
-        <v>9.9999999999999915E-3</v>
+        <v>9.9999999999999447E-3</v>
       </c>
       <c r="O46" s="29">
         <f t="shared" ref="O46" si="68">O45/O$27</f>
-        <v>8.4999999999999909E-2</v>
+        <v>8.500000000000002E-2</v>
       </c>
       <c r="P46" s="29">
         <f t="shared" ref="P46" si="69">P45/P$27</f>
-        <v>0.14999999999999991</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="47" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2928,27 +2928,27 @@
       </c>
       <c r="K48" s="28">
         <f t="shared" si="70"/>
-        <v>-861.4990424098296</v>
+        <v>-874.55205820391893</v>
       </c>
       <c r="L48" s="28">
         <f t="shared" si="70"/>
-        <v>-469.59916135658227</v>
+        <v>-484.16296110509347</v>
       </c>
       <c r="M48" s="28">
         <f t="shared" si="70"/>
-        <v>204.40056446427297</v>
+        <v>210.73969181863367</v>
       </c>
       <c r="N48" s="28">
         <f t="shared" si="70"/>
-        <v>1214.8760983616121</v>
+        <v>1232.0197020223588</v>
       </c>
       <c r="O48" s="28">
         <f t="shared" si="70"/>
-        <v>2501.6463680641409</v>
+        <v>2536.9481028593846</v>
       </c>
       <c r="P48" s="28">
         <f t="shared" si="70"/>
-        <v>3941.4255866978765</v>
+        <v>3997.044623246381</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="K49" s="29">
         <f t="shared" si="71"/>
-        <v>-0.13933781254190727</v>
+        <v>-0.13933781254190741</v>
       </c>
       <c r="L49" s="29">
         <f t="shared" si="71"/>
-        <v>-5.9337812541907314E-2</v>
+        <v>-5.933781254190728E-2</v>
       </c>
       <c r="M49" s="29">
         <f t="shared" si="71"/>
-        <v>2.0662187458092767E-2</v>
+        <v>2.0662187458092764E-2</v>
       </c>
       <c r="N49" s="29">
         <f t="shared" si="71"/>
-        <v>0.10066218745809269</v>
+        <v>0.10066218745809262</v>
       </c>
       <c r="O49" s="29">
         <f t="shared" si="71"/>
-        <v>0.17566218745809259</v>
+        <v>0.1756621874580927</v>
       </c>
       <c r="P49" s="29">
         <f t="shared" si="71"/>
-        <v>0.24066218745809256</v>
+        <v>0.24066218745809267</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3043,27 +3043,27 @@
       </c>
       <c r="K51" s="28">
         <f>K27*(AVERAGE(E52:J52))</f>
-        <v>229.99852912636032</v>
+        <v>233.48335532524459</v>
       </c>
       <c r="L51" s="28">
         <f t="shared" ref="L51:P51" si="72">L27*(AVERAGE(F52:K52))</f>
-        <v>326.7399643418118</v>
+        <v>336.87323501623831</v>
       </c>
       <c r="M51" s="28">
         <f t="shared" si="72"/>
-        <v>464.15173453552876</v>
+        <v>478.5465918329138</v>
       </c>
       <c r="N51" s="28">
         <f t="shared" si="72"/>
-        <v>588.74053948915059</v>
+        <v>597.04849326454246</v>
       </c>
       <c r="O51" s="28">
         <f t="shared" si="72"/>
-        <v>640.79224889821023</v>
+        <v>649.83472521230112</v>
       </c>
       <c r="P51" s="28">
         <f t="shared" si="72"/>
-        <v>704.48626999338819</v>
+        <v>714.42755817371585</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3156,27 +3156,27 @@
       </c>
       <c r="K54" s="28">
         <f>K27*(AVERAGE(E55:J55))</f>
-        <v>-6.8675689948050493</v>
+        <v>-6.9716230704839139</v>
       </c>
       <c r="L54" s="28">
         <f t="shared" ref="L54:P54" si="84">L27*(AVERAGE(F55:K55))</f>
-        <v>-8.8965782841847538</v>
+        <v>-9.1724901580550693</v>
       </c>
       <c r="M54" s="28">
         <f t="shared" si="84"/>
-        <v>-52.115717097333928</v>
+        <v>-53.731995255418859</v>
       </c>
       <c r="N54" s="28">
         <f t="shared" si="84"/>
-        <v>-27.860736231070675</v>
+        <v>-28.253890249234537</v>
       </c>
       <c r="O54" s="28">
         <f t="shared" si="84"/>
-        <v>-76.317343056114836</v>
+        <v>-77.394287679158936</v>
       </c>
       <c r="P54" s="28">
         <f t="shared" si="84"/>
-        <v>-75.792948913076572</v>
+        <v>-76.86249360014169</v>
       </c>
     </row>
     <row r="55" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3275,27 +3275,27 @@
       </c>
       <c r="K57" s="28">
         <f t="shared" ref="K57:P57" si="97">K45+K51+K54</f>
-        <v>-1198.9150454684443</v>
+        <v>-1217.0804249452399</v>
       </c>
       <c r="L57" s="28">
         <f t="shared" si="97"/>
-        <v>-869.25588818237281</v>
+        <v>-896.21434494181653</v>
       </c>
       <c r="M57" s="28">
         <f t="shared" si="97"/>
-        <v>-280.43855920180437</v>
+        <v>-289.13587247250439</v>
       </c>
       <c r="N57" s="28">
         <f t="shared" si="97"/>
-        <v>681.56822947247986</v>
+        <v>691.18611199530721</v>
       </c>
       <c r="O57" s="28">
         <f t="shared" si="97"/>
-        <v>1774.979820772526</v>
+        <v>1800.0272726025428</v>
       </c>
       <c r="P57" s="28">
         <f t="shared" si="97"/>
-        <v>3085.3062366744221</v>
+        <v>3128.8442298614737</v>
       </c>
     </row>
     <row r="58" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3328,27 +3328,27 @@
       </c>
       <c r="K58" s="29">
         <f t="shared" ref="K58" si="103">K57/K$27</f>
-        <v>-0.19391106853916132</v>
+        <v>-0.19391106853916146</v>
       </c>
       <c r="L58" s="29">
         <f t="shared" ref="L58" si="104">L57/L$27</f>
-        <v>-0.1098378088983608</v>
+        <v>-0.10983780889836077</v>
       </c>
       <c r="M58" s="29">
         <f t="shared" ref="M58" si="105">M57/M$27</f>
-        <v>-2.8348620738363667E-2</v>
+        <v>-2.8348620738363677E-2</v>
       </c>
       <c r="N58" s="29">
         <f t="shared" ref="N58" si="106">N57/N$27</f>
-        <v>5.6473371213051592E-2</v>
+        <v>5.6473371213051543E-2</v>
       </c>
       <c r="O58" s="29">
         <f t="shared" ref="O58" si="107">O57/O$27</f>
-        <v>0.12463665608027327</v>
+        <v>0.12463665608027341</v>
       </c>
       <c r="P58" s="29">
         <f t="shared" ref="P58" si="108">P57/P$27</f>
-        <v>0.18838781338460883</v>
+        <v>0.18838781338460889</v>
       </c>
     </row>
     <row r="60" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3387,15 +3387,15 @@
       </c>
       <c r="N60" s="7">
         <f>MAX(0,N57*0.05)</f>
-        <v>34.078411473623994</v>
+        <v>34.559305599765359</v>
       </c>
       <c r="O60" s="7">
         <f>MAX(0,O57*0.1)</f>
-        <v>177.4979820772526</v>
+        <v>180.00272726025429</v>
       </c>
       <c r="P60" s="7">
         <f t="shared" si="109"/>
-        <v>462.79593550116329</v>
+        <v>469.32663447922101</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3474,27 +3474,27 @@
       </c>
       <c r="K63" s="28">
         <f t="shared" ref="K63:P63" si="112">K57+K60</f>
-        <v>-1198.9150454684443</v>
+        <v>-1217.0804249452399</v>
       </c>
       <c r="L63" s="28">
         <f t="shared" si="112"/>
-        <v>-869.25588818237281</v>
+        <v>-896.21434494181653</v>
       </c>
       <c r="M63" s="28">
         <f t="shared" si="112"/>
-        <v>-280.43855920180437</v>
+        <v>-289.13587247250439</v>
       </c>
       <c r="N63" s="28">
         <f t="shared" si="112"/>
-        <v>715.64664094610384</v>
+        <v>725.74541759507258</v>
       </c>
       <c r="O63" s="28">
         <f t="shared" si="112"/>
-        <v>1952.4778028497785</v>
+        <v>1980.029999862797</v>
       </c>
       <c r="P63" s="28">
         <f t="shared" si="112"/>
-        <v>3548.1021721755851</v>
+        <v>3598.1708643406946</v>
       </c>
     </row>
     <row r="64" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3527,27 +3527,27 @@
       </c>
       <c r="K64" s="29">
         <f t="shared" ref="K64" si="118">K63/K$27</f>
-        <v>-0.19391106853916132</v>
+        <v>-0.19391106853916146</v>
       </c>
       <c r="L64" s="29">
         <f t="shared" ref="L64" si="119">L63/L$27</f>
-        <v>-0.1098378088983608</v>
+        <v>-0.10983780889836077</v>
       </c>
       <c r="M64" s="29">
         <f t="shared" ref="M64" si="120">M63/M$27</f>
-        <v>-2.8348620738363667E-2</v>
+        <v>-2.8348620738363677E-2</v>
       </c>
       <c r="N64" s="29">
         <f t="shared" ref="N64" si="121">N63/N$27</f>
-        <v>5.9297039773704173E-2</v>
+        <v>5.9297039773704117E-2</v>
       </c>
       <c r="O64" s="29">
         <f t="shared" ref="O64" si="122">O63/O$27</f>
-        <v>0.13710032168830061</v>
+        <v>0.13710032168830075</v>
       </c>
       <c r="P64" s="29">
         <f t="shared" ref="P64" si="123">P63/P$27</f>
-        <v>0.21664598539230012</v>
+        <v>0.21664598539230021</v>
       </c>
     </row>
     <row r="65" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3706,27 +3706,27 @@
       </c>
       <c r="K69" s="31">
         <f>K63/K66</f>
-        <v>-3.4999158179028078</v>
+        <v>-3.5529448454467927</v>
       </c>
       <c r="L69" s="31">
         <f t="shared" ref="L69:P69" si="133">L63/L66</f>
-        <v>-2.5000620470496426</v>
+        <v>-2.5775971152701684</v>
       </c>
       <c r="M69" s="31">
         <f t="shared" si="133"/>
-        <v>-0.79464806637451446</v>
+        <v>-0.81929269153906537</v>
       </c>
       <c r="N69" s="32">
         <f t="shared" si="133"/>
-        <v>1.997881376968069</v>
+        <v>2.026074282017496</v>
       </c>
       <c r="O69" s="31">
         <f t="shared" si="133"/>
-        <v>5.3702082135647968</v>
+        <v>5.4459893745516759</v>
       </c>
       <c r="P69" s="31">
         <f t="shared" si="133"/>
-        <v>9.6146857559086634</v>
+        <v>9.7503624410819327</v>
       </c>
     </row>
     <row r="71" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3815,27 +3815,27 @@
       </c>
       <c r="K73" s="7">
         <f>K27*(AVERAGE($H$74:$J$74))</f>
-        <v>288.76738957906201</v>
+        <v>293.14265305753264</v>
       </c>
       <c r="L73" s="7">
         <f t="shared" ref="L73:P73" si="134">L27*(AVERAGE($H$74:$J$74))</f>
-        <v>369.62225866119934</v>
+        <v>381.08544897479243</v>
       </c>
       <c r="M73" s="7">
         <f t="shared" si="134"/>
-        <v>462.02782332649923</v>
+        <v>476.35681121849058</v>
       </c>
       <c r="N73" s="7">
         <f t="shared" si="134"/>
-        <v>563.67394445832906</v>
+        <v>571.62817346218867</v>
       </c>
       <c r="O73" s="7">
         <f t="shared" si="134"/>
-        <v>665.13525446082815</v>
+        <v>674.52124468538261</v>
       </c>
       <c r="P73" s="7">
         <f t="shared" si="134"/>
-        <v>764.90554262995238</v>
+        <v>775.69943138818985</v>
       </c>
     </row>
     <row r="74" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="K74" s="10">
         <f t="shared" ref="K74:P74" si="135">K73/K$27</f>
-        <v>4.6704888127132943E-2</v>
+        <v>4.6704888127132936E-2</v>
       </c>
       <c r="L74" s="10">
         <f t="shared" si="135"/>
@@ -3930,27 +3930,27 @@
       </c>
       <c r="K77" s="7">
         <f>K$27*(AVERAGE($H78:$J$78))</f>
-        <v>271.77957361110805</v>
+        <v>275.89744593854914</v>
       </c>
       <c r="L77" s="7">
         <f>L$27*(AVERAGE($H78:$J$78))</f>
-        <v>347.87785422221833</v>
+        <v>358.66667972011385</v>
       </c>
       <c r="M77" s="7">
         <f>M$27*(AVERAGE($H78:$J$78))</f>
-        <v>434.84731777777296</v>
+        <v>448.3333496501424</v>
       </c>
       <c r="N77" s="7">
         <f>N$27*(AVERAGE($H78:$J$78))</f>
-        <v>530.51372768888302</v>
+        <v>538.00001958017083</v>
       </c>
       <c r="O77" s="7">
         <f>O$27*(AVERAGE($H78:$J$78))</f>
-        <v>626.00619867288185</v>
+        <v>634.84002310460153</v>
       </c>
       <c r="P77" s="7">
         <f>P$27*(AVERAGE($H78:$J$78))</f>
-        <v>719.90712847381405</v>
+        <v>730.06602657029168</v>
       </c>
     </row>
     <row r="78" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="K78" s="10">
         <f t="shared" ref="K78:P78" si="136">K77/K$27</f>
-        <v>4.3957299330959737E-2</v>
+        <v>4.3957299330959751E-2</v>
       </c>
       <c r="L78" s="10">
         <f t="shared" si="136"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="N78" s="10">
         <f t="shared" si="136"/>
-        <v>4.3957299330959751E-2</v>
+        <v>4.3957299330959744E-2</v>
       </c>
       <c r="O78" s="10">
         <f t="shared" si="136"/>
@@ -4018,27 +4018,27 @@
       </c>
       <c r="K80" s="7">
         <f>K$27*(AVERAGE($H81:$J$81))</f>
-        <v>138.57535783245635</v>
+        <v>140.67498446628144</v>
       </c>
       <c r="L80" s="7">
         <f>L$27*(AVERAGE($H81:$J$81))</f>
-        <v>177.37645802554411</v>
+        <v>182.87747980616589</v>
       </c>
       <c r="M80" s="7">
         <f>M$27*(AVERAGE($H81:$J$81))</f>
-        <v>221.72057253193015</v>
+        <v>228.59684975770736</v>
       </c>
       <c r="N80" s="7">
         <f>N$27*(AVERAGE($H81:$J$81))</f>
-        <v>270.49909848895476</v>
+        <v>274.31621970924886</v>
       </c>
       <c r="O80" s="7">
         <f>O$27*(AVERAGE($H81:$J$81))</f>
-        <v>319.18893621696662</v>
+        <v>323.69313925691358</v>
       </c>
       <c r="P80" s="7">
         <f>P$27*(AVERAGE($H81:$J$81))</f>
-        <v>367.0672766495116</v>
+        <v>372.24711014545056</v>
       </c>
     </row>
     <row r="81" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="N81" s="10">
         <f t="shared" si="137"/>
-        <v>2.2413010673320057E-2</v>
+        <v>2.241301067332006E-2</v>
       </c>
       <c r="O81" s="10">
         <f t="shared" si="137"/>
@@ -4106,27 +4106,27 @@
       </c>
       <c r="K83" s="12">
         <f>(K27-J27)*0.3</f>
-        <v>449.658816</v>
+        <v>477.76249200000007</v>
       </c>
       <c r="L83" s="12">
         <f>(L27-K27)*0.25</f>
-        <v>432.79661039999996</v>
+        <v>470.73657300000013</v>
       </c>
       <c r="M83" s="12">
         <f>(M27-L27)*0.2</f>
-        <v>395.69975808000021</v>
+        <v>407.9716966000002</v>
       </c>
       <c r="N83" s="12">
         <f>(N27-M27)*0.15</f>
-        <v>326.45230041599996</v>
+        <v>305.97877245000001</v>
       </c>
       <c r="O83" s="12">
         <f>(O27-N27)*0.1</f>
-        <v>217.23916718591991</v>
+        <v>220.30471616399993</v>
       </c>
       <c r="P83" s="12">
         <f>(P27-O27)*0.05</f>
-        <v>106.80925719974394</v>
+        <v>108.31648544729988</v>
       </c>
     </row>
     <row r="84" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4150,11 +4150,11 @@
       </c>
       <c r="K84" s="10">
         <f t="shared" ref="K84:P84" si="138">K83/K$27</f>
-        <v>7.2727272727272724E-2</v>
+        <v>7.6119402985074636E-2</v>
       </c>
       <c r="L84" s="10">
         <f t="shared" si="138"/>
-        <v>5.4687499999999993E-2</v>
+        <v>5.7692307692307702E-2</v>
       </c>
       <c r="M84" s="10">
         <f t="shared" si="138"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="N84" s="10">
         <f t="shared" si="138"/>
-        <v>2.7049180327868849E-2</v>
+        <v>2.4999999999999998E-2</v>
       </c>
       <c r="O84" s="10">
         <f t="shared" si="138"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="P84" s="10">
         <f t="shared" si="138"/>
-        <v>6.5217391304347797E-3</v>
+        <v>6.5217391304347762E-3</v>
       </c>
     </row>
     <row r="85" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4312,27 +4312,27 @@
       </c>
       <c r="K89" s="28">
         <f t="shared" ref="K89:P89" si="142">K27</f>
-        <v>6182.80872</v>
+        <v>6276.4876400000003</v>
       </c>
       <c r="L89" s="28">
         <f t="shared" si="142"/>
-        <v>7913.9951615999998</v>
+        <v>8159.4339320000008</v>
       </c>
       <c r="M89" s="28">
         <f t="shared" si="142"/>
-        <v>9892.4939520000007</v>
+        <v>10199.292415000002</v>
       </c>
       <c r="N89" s="28">
         <f t="shared" si="142"/>
-        <v>12068.842621440001</v>
+        <v>12239.150898000002</v>
       </c>
       <c r="O89" s="28">
         <f t="shared" si="142"/>
-        <v>14241.2342932992</v>
+        <v>14442.198059640001</v>
       </c>
       <c r="P89" s="28">
         <f t="shared" si="142"/>
-        <v>16377.419437294078</v>
+        <v>16608.527768585998</v>
       </c>
     </row>
     <row r="90" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4367,11 +4367,11 @@
       </c>
       <c r="K90" s="10">
         <f t="shared" ref="K90:P90" si="144">K28</f>
-        <v>0.32</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="L90" s="10">
         <f t="shared" si="144"/>
-        <v>0.27999999999999997</v>
+        <v>0.3000000000000001</v>
       </c>
       <c r="M90" s="10">
         <f t="shared" si="144"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="N90" s="10">
         <f t="shared" si="144"/>
-        <v>0.21999999999999997</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="O90" s="10">
         <f t="shared" si="144"/>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="P90" s="10">
         <f t="shared" si="144"/>
-        <v>0.14999999999999991</v>
+        <v>0.14999999999999983</v>
       </c>
     </row>
     <row r="91" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4434,27 +4434,27 @@
       </c>
       <c r="K92" s="28">
         <f t="shared" ref="K92:P92" si="146">K45</f>
-        <v>-1422.0460055999997</v>
+        <v>-1443.5921572000007</v>
       </c>
       <c r="L92" s="28">
         <f t="shared" si="146"/>
-        <v>-1187.0992742399999</v>
+        <v>-1223.9150897999998</v>
       </c>
       <c r="M92" s="28">
         <f t="shared" si="146"/>
-        <v>-692.47457663999921</v>
+        <v>-713.95046904999936</v>
       </c>
       <c r="N92" s="28">
         <f t="shared" si="146"/>
-        <v>120.6884262143999</v>
+        <v>122.39150897999934</v>
       </c>
       <c r="O92" s="28">
         <f t="shared" si="146"/>
-        <v>1210.5049149304307</v>
+        <v>1227.5868350694004</v>
       </c>
       <c r="P92" s="28">
         <f t="shared" si="146"/>
-        <v>2456.6129155941103</v>
+        <v>2491.2791652878996</v>
       </c>
     </row>
     <row r="93" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="K93" s="29">
         <f t="shared" ref="K93:P93" si="148">K46</f>
-        <v>-0.22999999999999995</v>
+        <v>-0.23000000000000009</v>
       </c>
       <c r="L93" s="29">
         <f t="shared" si="148"/>
-        <v>-0.15</v>
+        <v>-0.14999999999999997</v>
       </c>
       <c r="M93" s="29">
         <f t="shared" si="148"/>
-        <v>-6.999999999999991E-2</v>
+        <v>-6.9999999999999923E-2</v>
       </c>
       <c r="N93" s="29">
         <f t="shared" si="148"/>
-        <v>9.9999999999999915E-3</v>
+        <v>9.9999999999999447E-3</v>
       </c>
       <c r="O93" s="29">
         <f t="shared" si="148"/>
-        <v>8.4999999999999909E-2</v>
+        <v>8.500000000000002E-2</v>
       </c>
       <c r="P93" s="29">
         <f t="shared" si="148"/>
-        <v>0.14999999999999991</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="94" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4563,15 +4563,15 @@
       </c>
       <c r="N95" s="28">
         <f t="shared" si="150"/>
-        <v>34.078411473623994</v>
+        <v>34.559305599765359</v>
       </c>
       <c r="O95" s="28">
         <f t="shared" si="150"/>
-        <v>177.4979820772526</v>
+        <v>180.00272726025429</v>
       </c>
       <c r="P95" s="28">
         <f t="shared" si="150"/>
-        <v>462.79593550116329</v>
+        <v>469.32663447922101</v>
       </c>
     </row>
     <row r="96" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4659,27 +4659,27 @@
       </c>
       <c r="K98" s="28">
         <f t="shared" ref="K98:P98" si="154">K92-K95</f>
-        <v>-1422.0460055999997</v>
+        <v>-1443.5921572000007</v>
       </c>
       <c r="L98" s="28">
         <f t="shared" si="154"/>
-        <v>-1187.0992742399999</v>
+        <v>-1223.9150897999998</v>
       </c>
       <c r="M98" s="28">
         <f t="shared" si="154"/>
-        <v>-692.47457663999921</v>
+        <v>-713.95046904999936</v>
       </c>
       <c r="N98" s="28">
         <f t="shared" si="154"/>
-        <v>86.61001474077591</v>
+        <v>87.832203380233977</v>
       </c>
       <c r="O98" s="28">
         <f t="shared" si="154"/>
-        <v>1033.0069328531781</v>
+        <v>1047.5841078091462</v>
       </c>
       <c r="P98" s="28">
         <f t="shared" si="154"/>
-        <v>1993.816980092947</v>
+        <v>2021.9525308086786</v>
       </c>
     </row>
     <row r="100" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4703,27 +4703,27 @@
       </c>
       <c r="K100" s="7">
         <f t="shared" ref="K100:P100" si="155">K73+K77</f>
-        <v>560.54696319017012</v>
+        <v>569.04009899608172</v>
       </c>
       <c r="L100" s="7">
         <f t="shared" si="155"/>
-        <v>717.50011288341761</v>
+        <v>739.75212869490633</v>
       </c>
       <c r="M100" s="7">
         <f t="shared" si="155"/>
-        <v>896.87514110427219</v>
+        <v>924.69016086863303</v>
       </c>
       <c r="N100" s="7">
         <f t="shared" si="155"/>
-        <v>1094.1876721472122</v>
+        <v>1109.6281930423595</v>
       </c>
       <c r="O100" s="7">
         <f t="shared" si="155"/>
-        <v>1291.14145313371</v>
+        <v>1309.3612677899841</v>
       </c>
       <c r="P100" s="7">
         <f t="shared" si="155"/>
-        <v>1484.8126711037664</v>
+        <v>1505.7654579584814</v>
       </c>
     </row>
     <row r="101" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="K101" s="10">
         <f t="shared" ref="K101:P101" si="156">K100/K$27</f>
-        <v>9.0662187458092694E-2</v>
+        <v>9.066218745809268E-2</v>
       </c>
       <c r="L101" s="10">
         <f t="shared" si="156"/>
@@ -4757,11 +4757,11 @@
       </c>
       <c r="M101" s="10">
         <f t="shared" si="156"/>
-        <v>9.066218745809268E-2</v>
+        <v>9.0662187458092694E-2</v>
       </c>
       <c r="N101" s="10">
         <f t="shared" si="156"/>
-        <v>9.0662187458092694E-2</v>
+        <v>9.066218745809268E-2</v>
       </c>
       <c r="O101" s="10">
         <f t="shared" si="156"/>
@@ -4793,27 +4793,27 @@
       </c>
       <c r="K103" s="7">
         <f t="shared" ref="K103:P103" si="158">K80</f>
-        <v>138.57535783245635</v>
+        <v>140.67498446628144</v>
       </c>
       <c r="L103" s="7">
         <f t="shared" si="158"/>
-        <v>177.37645802554411</v>
+        <v>182.87747980616589</v>
       </c>
       <c r="M103" s="7">
         <f t="shared" si="158"/>
-        <v>221.72057253193015</v>
+        <v>228.59684975770736</v>
       </c>
       <c r="N103" s="7">
         <f t="shared" si="158"/>
-        <v>270.49909848895476</v>
+        <v>274.31621970924886</v>
       </c>
       <c r="O103" s="7">
         <f t="shared" si="158"/>
-        <v>319.18893621696662</v>
+        <v>323.69313925691358</v>
       </c>
       <c r="P103" s="7">
         <f t="shared" si="158"/>
-        <v>367.0672766495116</v>
+        <v>372.24711014545056</v>
       </c>
       <c r="Q103" s="7"/>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="N104" s="10">
         <f t="shared" si="159"/>
-        <v>2.2413010673320057E-2</v>
+        <v>2.241301067332006E-2</v>
       </c>
       <c r="O104" s="10">
         <f t="shared" si="159"/>
@@ -4884,27 +4884,27 @@
       </c>
       <c r="K106" s="12">
         <f t="shared" ref="K106:P106" si="160">K83</f>
-        <v>449.658816</v>
+        <v>477.76249200000007</v>
       </c>
       <c r="L106" s="12">
         <f t="shared" si="160"/>
-        <v>432.79661039999996</v>
+        <v>470.73657300000013</v>
       </c>
       <c r="M106" s="12">
         <f t="shared" si="160"/>
-        <v>395.69975808000021</v>
+        <v>407.9716966000002</v>
       </c>
       <c r="N106" s="12">
         <f t="shared" si="160"/>
-        <v>326.45230041599996</v>
+        <v>305.97877245000001</v>
       </c>
       <c r="O106" s="12">
         <f t="shared" si="160"/>
-        <v>217.23916718591991</v>
+        <v>220.30471616399993</v>
       </c>
       <c r="P106" s="12">
         <f t="shared" si="160"/>
-        <v>106.80925719974394</v>
+        <v>108.31648544729988</v>
       </c>
     </row>
     <row r="107" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4930,11 +4930,11 @@
       </c>
       <c r="K107" s="10">
         <f t="shared" ref="K107:P107" si="161">K106/K$27</f>
-        <v>7.2727272727272724E-2</v>
+        <v>7.6119402985074636E-2</v>
       </c>
       <c r="L107" s="10">
         <f t="shared" si="161"/>
-        <v>5.4687499999999993E-2</v>
+        <v>5.7692307692307702E-2</v>
       </c>
       <c r="M107" s="10">
         <f t="shared" si="161"/>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="N107" s="10">
         <f t="shared" si="161"/>
-        <v>2.7049180327868849E-2</v>
+        <v>2.4999999999999998E-2</v>
       </c>
       <c r="O107" s="10">
         <f t="shared" si="161"/>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="P107" s="10">
         <f t="shared" si="161"/>
-        <v>6.5217391304347797E-3</v>
+        <v>6.5217391304347762E-3</v>
       </c>
     </row>
     <row r="108" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="K110" s="10">
         <f t="shared" ref="K110:P110" si="162">K109/K$27</f>
-        <v>0.25870879602434149</v>
+        <v>0.25484747071054537</v>
       </c>
       <c r="L110" s="10">
         <f t="shared" si="162"/>
-        <v>0.2021162468940168</v>
+        <v>0.19603651593118873</v>
       </c>
       <c r="M110" s="10">
         <f t="shared" si="162"/>
-        <v>0.16169299751521343</v>
+        <v>0.15682921274495096</v>
       </c>
       <c r="N110" s="10">
         <f t="shared" si="162"/>
-        <v>0.13253524386492904</v>
+        <v>0.13069101062079247</v>
       </c>
       <c r="O110" s="10">
         <f t="shared" si="162"/>
-        <v>0.11231800327536361</v>
+        <v>0.11075509374643432</v>
       </c>
       <c r="P110" s="10">
         <f t="shared" si="162"/>
-        <v>9.7667828935098802E-2</v>
+        <v>9.630877717081246E-2</v>
       </c>
     </row>
     <row r="112" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5072,27 +5072,27 @@
       </c>
       <c r="K112" s="28">
         <f t="shared" si="163"/>
-        <v>-550.41558424228595</v>
+        <v>-537.46455067020031</v>
       </c>
       <c r="L112" s="28">
         <f t="shared" si="163"/>
-        <v>-214.17900898212645</v>
+        <v>-196.3038679112592</v>
       </c>
       <c r="M112" s="28">
         <f t="shared" si="163"/>
-        <v>378.37975001234304</v>
+        <v>390.11453866092654</v>
       </c>
       <c r="N112" s="28">
         <f t="shared" si="163"/>
-        <v>1236.7508888150332</v>
+        <v>1229.1229491633446</v>
       </c>
       <c r="O112" s="28">
         <f t="shared" si="163"/>
-        <v>2222.1986169558413</v>
+        <v>2253.5569525062165</v>
       </c>
       <c r="P112" s="28">
         <f>P98+P100-P103+P106</f>
-        <v>3218.3716317469457</v>
+        <v>3263.7873640690091</v>
       </c>
       <c r="Q112" s="7"/>
       <c r="R112" s="7"/>
@@ -5126,27 +5126,27 @@
       </c>
       <c r="K113" s="29">
         <f t="shared" ref="K113:P113" si="164">K112/K$27</f>
-        <v>-8.90235504879546E-2</v>
+        <v>-8.5631420230152841E-2</v>
       </c>
       <c r="L113" s="29">
         <f t="shared" si="164"/>
-        <v>-2.7063323215227381E-2</v>
+        <v>-2.4058515522919634E-2</v>
       </c>
       <c r="M113" s="29">
         <f t="shared" si="164"/>
-        <v>3.8249176784772729E-2</v>
+        <v>3.8249176784772722E-2</v>
       </c>
       <c r="N113" s="29">
         <f t="shared" si="164"/>
-        <v>0.10247468855198889</v>
+        <v>0.10042550822411998</v>
       </c>
       <c r="O113" s="29">
         <f t="shared" si="164"/>
-        <v>0.15603974846488078</v>
+        <v>0.15603974846488089</v>
       </c>
       <c r="P113" s="29">
         <f t="shared" si="164"/>
-        <v>0.19651274390751597</v>
+        <v>0.19651274390751605</v>
       </c>
     </row>
     <row r="114" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5190,27 +5190,27 @@
       <c r="J116" s="7"/>
       <c r="K116" s="34">
         <f t="shared" ref="K116:P116" si="165">K112/(1+$U$7)^K115</f>
-        <v>-541.4708966229133</v>
+        <v>-528.73032756703458</v>
       </c>
       <c r="L116" s="34">
         <f t="shared" si="165"/>
-        <v>-190.97111489257139</v>
+        <v>-175.03287876294962</v>
       </c>
       <c r="M116" s="34">
         <f t="shared" si="165"/>
-        <v>305.79124459796031</v>
+        <v>315.2748272310883</v>
       </c>
       <c r="N116" s="34">
         <f t="shared" si="165"/>
-        <v>905.91150163836994</v>
+        <v>900.32408841977986</v>
       </c>
       <c r="O116" s="34">
         <f t="shared" si="165"/>
-        <v>1475.342309628292</v>
+        <v>1496.1614564156148</v>
       </c>
       <c r="P116" s="34">
         <f t="shared" si="165"/>
-        <v>1936.6560530612396</v>
+        <v>1963.9849830201426</v>
       </c>
     </row>
     <row r="117" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C2" s="36" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">_FV(B2,"Price")</f>
-        <v>255.55</v>
+        <v>325.43</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
